--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,23 +774,23 @@
       <c r="C4" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F4" s="10" t="n">
+      <c r="D4" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>4.2</v>
@@ -793,32 +802,32 @@
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>30</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -827,7 +836,7 @@
         <v>27.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>9.699999999999999</v>
@@ -846,19 +855,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>21.5</v>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.3</v>
@@ -876,19 +885,19 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>96.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.3</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
@@ -897,13 +906,13 @@
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>18.9</v>
@@ -912,7 +921,7 @@
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>3.6</v>
@@ -931,35 +940,37 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>431.6</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="12" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>19</v>
+      <c r="M6" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
@@ -968,7 +979,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
@@ -982,7 +993,7 @@
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -995,10 +1006,10 @@
         <v>26.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1016,20 +1027,20 @@
       <c r="C7" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>85</v>
+      <c r="E7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>14.8</v>
+      <c r="H7" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3.4</v>
@@ -1038,25 +1049,25 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>17.3</v>
-      </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+      <c r="Q7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
@@ -1065,25 +1076,25 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>5.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>27.6</v>
+        <v>6.6</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>4.1</v>
+        <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>75.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1099,46 +1110,46 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>26.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>18.5</v>
+        <v>24.5</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.6</v>
+      <c r="M8" s="8" t="n">
+        <v>865.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>87.2</v>
+        <v>82.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
@@ -1153,22 +1164,22 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>212.4</v>
+        <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>90.2</v>
+        <v>96.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1184,25 +1195,23 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6663.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>22.5</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="11" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>60.1</v>
+        <v>611.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80.5</v>
+        <v>86.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1214,7 +1223,7 @@
         <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
@@ -1223,7 +1232,7 @@
         <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>138.8</v>
@@ -1232,7 +1241,7 @@
         <v>11.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>344.1</v>
+        <v>31.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1244,13 +1253,13 @@
         <v>126.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2.8</v>
@@ -1269,38 +1278,40 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="12" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>44.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>17.6</v>
+      <c r="M10" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>88.2</v>
@@ -1309,31 +1320,31 @@
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>27.8</v>
+        <v>82.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>26.4</v>
+        <v>2.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>80.5</v>
+        <v>806.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>6.6</v>
@@ -1352,19 +1363,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="10" t="n">
+        <v>445.6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
@@ -1373,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>31.3</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1384,7 +1395,9 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
@@ -1394,14 +1407,14 @@
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>5.7</v>
@@ -1412,11 +1425,11 @@
       <c r="W11" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>97.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.8</v>
@@ -1437,17 +1450,17 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F12" s="10" t="n">
+      <c r="D12" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.5</v>
+        <v>84.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
@@ -1468,18 +1481,18 @@
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>61.1</v>
+        <v>21.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1489,13 +1502,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.3</v>
+        <v>53.3</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>24.7</v>
+        <v>4.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>30.4</v>
@@ -1504,7 +1517,7 @@
         <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1520,22 +1533,22 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>256.7</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F13" s="10" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
@@ -1544,7 +1557,7 @@
         <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1553,22 +1566,22 @@
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>32.7</v>
+      <c r="S13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1576,17 +1589,17 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>93.8</v>
+        <v>43.2</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1605,22 +1618,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12.9</v>
+      <c r="E14" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
@@ -1629,16 +1642,16 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+        <v>57.2</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.90000000000001</v>
@@ -1650,10 +1663,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1671,7 +1684,7 @@
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1692,14 +1705,14 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>24.9</v>
+      <c r="D15" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>44.1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
@@ -1714,16 +1727,16 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>20.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>88.8</v>
@@ -1747,19 +1760,19 @@
         <v>14.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>24.5</v>
+        <v>4.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>74</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1775,13 +1788,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>149.9</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>99.09999999999999</v>
+        <v>929.1</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>124.7</v>
@@ -1802,47 +1815,49 @@
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>100.9</v>
+        <v>160.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>21122.2</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83</v>
+        <v>23.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>445.1</v>
+        <v>42.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>53.1</v>
+        <v>533.4</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>451.1</v>
+        <v>46.4</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>315.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>455.1</v>
+        <v>45.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1857,8 +1872,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>399.2</v>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+3986
+</t>
+        </is>
       </c>
       <c r="D17" s="10" t="n">
         <v>30</v>
@@ -1867,19 +1886,19 @@
         <v>19.8</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>24.9</v>
+        <v>14.4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n">
@@ -1889,7 +1908,7 @@
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>88.8</v>
@@ -1901,30 +1920,32 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>28.5</v>
+        <v>22.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>42.8</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>43.2</v>
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1939,58 +1960,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>137.3</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>24.9</v>
+        <v>43.2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>64.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>81.8</v>
+        <v>11.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>21.9</v>
+        <v>82</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.2</v>
+        <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.1</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>4.4</v>
@@ -2005,10 +2026,14 @@
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>2.6</v>
+        <v>24.1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+8 179
+</t>
+        </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2026,19 +2051,19 @@
       <c r="C19" s="3" t="n">
         <v>423.9</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="12" t="n">
         <v>25.4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2048,16 +2073,16 @@
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>21.5</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>87.5</v>
@@ -2069,7 +2094,7 @@
         <v>31.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
+        <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>25.3</v>
@@ -2081,19 +2106,27 @@
         <v>21.7</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>25.8</v>
+        <v>85.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>6.2</v>
+        <v>2</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+44
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+818
+</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2109,34 +2142,39 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>41.3</v>
+        <v>3561.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+1 8 4
+7
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>18.8</v>
@@ -2145,13 +2183,13 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>89</v>
+        <v>21.1</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>25.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>535.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
@@ -2160,7 +2198,7 @@
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>20.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>9.5</v>
@@ -2172,10 +2210,10 @@
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2194,20 +2232,18 @@
       <c r="C21" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="E21" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.2</v>
@@ -2216,13 +2252,13 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2237,28 +2273,32 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>21.7</v>
+        <v>41.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>531</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24.3</v>
+        <v>44.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>955.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+8111
+</t>
+        </is>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>250.4</v>
+        <v>850.1</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>4.5</v>
@@ -2277,22 +2317,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
+        <v>34</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.8</v>
+        <v>31.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
+        <v>12.2</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>84.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.3</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.1</v>
@@ -2304,16 +2344,16 @@
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>87.5</v>
+        <v>1.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>87</v>
+        <v>872</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>2.6</v>
@@ -2328,22 +2368,22 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>568.1</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>85.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2362,76 +2402,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>24.5</v>
+        <v>1985.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>653.4</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14.6</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.7</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>17.6</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.2</v>
+        <v>882.6</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
+        <v>438.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>215.4</v>
+        <v>2952.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>462.1</v>
+        <v>12.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>103.6</v>
+        <v>10.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>0.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2447,76 +2487,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>23</v>
+        <v>5851.1</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>60.3</v>
+        <v>3.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>85</v>
+        <v>12.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>49.2</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>95.2</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>88.2</v>
+        <v>12.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>96.5</v>
+        <v>1.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>437.2</v>
+        <v>872.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>46.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>19</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>215.4</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>462.1</v>
+        <v>4.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>103.6</v>
+        <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>28.7</v>
+        <v>0.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>411</v>
+        <v>0.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2532,76 +2570,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>81.61</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>24.6</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>45.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>87</v>
+        <v>18.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>19.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>21.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>29.2</v>
+        <v>324.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>23.8</v>
+        <v>1.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>59</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.4</v>
+        <v>7.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>22.1</v>
+        <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>85.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2617,49 +2655,49 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>34.1</v>
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>45.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>20.4</v>
+        <v>18.1</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>31.3</v>
+        <v>324.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.3</v>
@@ -2674,19 +2712,19 @@
         <v>19.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>0.4</v>
+        <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>22.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2702,28 +2740,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>329.8</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="12" t="n">
         <v>24.7</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.3</v>
@@ -2732,18 +2770,18 @@
         <v>19</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.4</v>
+        <v>12.6</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2753,16 +2791,16 @@
         <v>24.5</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.2</v>
+        <v>6.1</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>21.8</v>
+        <v>41.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>24.6</v>
@@ -2770,8 +2808,12 @@
       <c r="Y27" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z27" s="3" t="n">
-        <v>7.6</v>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+54
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2787,46 +2829,46 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>23.8</v>
+        <v>354.2</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>20.2</v>
+        <v>10.2</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.8</v>
+        <v>61.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>26</v>
@@ -2835,7 +2877,7 @@
         <v>21.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68.40000000000001</v>
@@ -2844,19 +2886,19 @@
         <v>10.6</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>23.2</v>
+        <v>63.5</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>20.8</v>
+        <v>6.2</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>808.1</v>
+        <v>8.1</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2874,44 +2916,44 @@
       <c r="C29" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="D29" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>239.6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.2</v>
@@ -2926,22 +2968,22 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2957,13 +2999,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>408.5</v>
+        <v>42.6</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>29.5</v>
+        <v>494.5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>20.4</v>
+        <v>61.3</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>24.9</v>
@@ -2972,22 +3014,22 @@
         <v>9.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.2</v>
+        <v>20.2</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>21.5</v>
@@ -2996,7 +3038,7 @@
         <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>28.6</v>
@@ -3011,10 +3053,10 @@
         <v>62.6</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>15.5</v>
+        <v>85.5</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>23</v>
@@ -3023,10 +3065,10 @@
         <v>26.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3042,61 +3084,61 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>97.8</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.5</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>954.4</v>
+        <v>25.4</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>3.2</v>
+        <v>93.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>113.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>441.9</v>
+        <v>44.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>138.5</v>
+        <v>38.5</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>43.8</v>
+        <v>3.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>22.7</v>
+        <v>18.7</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>332.8</v>
+        <v>334.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>64.3</v>
+        <v>0.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>23.1</v>
@@ -3108,10 +3150,10 @@
         <v>24.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>399.8</v>
+        <v>322.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3127,46 +3169,48 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>371.3</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>24.9</v>
+        <v>437.3</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>19.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>92.2</v>
+        <v>18.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>206.1</v>
+        <v>26.6</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3176,25 +3220,29 @@
         <v>24.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>122.1</v>
+        <v>12.9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>24.9</v>
+        <v>42.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.5</v>
+        <v>22.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+78
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3210,52 +3258,52 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E33" s="10" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.6</v>
+        <v>12.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.5</v>
+        <v>61.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31</v>
+        <v>0.1</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.4</v>
@@ -3267,19 +3315,19 @@
         <v>19.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.7</v>
+        <v>2.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>26.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3295,28 +3343,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="D34" s="11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>17.9</v>
+        <v>12.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3325,46 +3373,50 @@
         <v>20.9</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>32.9</v>
+        <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.9</v>
+        <v>2.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>26.1</v>
+        <v>2.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.8</v>
+        <v>45.5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>61.2</v>
+        <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>7.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+5
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3380,76 +3432,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>362.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>25.3</v>
+        <v>884.5</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
+      <c r="K35" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21</v>
+        <v>61.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>87.3</v>
+        <v>25.4</v>
       </c>
       <c r="P35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>25.5</v>
+      <c r="V35" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>23.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>27.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>83.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3465,76 +3515,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>22.6</v>
+        <v>398.9</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>24.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q36" s="3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>20.3</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>88.5</v>
+        <v>326.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3550,76 +3598,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>398.9</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>24.3</v>
+        <v>1683.5</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>35.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.6</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>120.6</v>
+        <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>21.7</v>
+        <v>117.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>89</v>
+        <v>432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>27</v>
+        <v>691.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.1</v>
+        <v>6.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>25.8</v>
+        <v>62.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>72.3</v>
+        <v>13.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>651.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>25</v>
+        <v>126.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>22.1</v>
+        <v>76.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>24.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.6</v>
+        <v>62.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3635,76 +3683,76 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>55.1</v>
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>163.5</v>
+        <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>44.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>437.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>399.6</v>
+        <v>3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>620.1</v>
+        <v>23.1</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>343.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>65.7</v>
+        <v>13.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>26.1</v>
+        <v>52.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>44.4</v>
+        <v>0.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>4.4</v>
+        <v>35.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>396.6</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3720,76 +3768,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>25.1</v>
+        <v>42.7</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>15.7</v>
+        <v>3.4</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>25.1</v>
+        <v>41.5</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>87.5</v>
+        <v>2.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.2</v>
+        <v>31.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.7</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>95.2</v>
+        <v>76.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>79.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3805,76 +3853,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>48.4</v>
+        <v>4.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>19.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.7</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>2.5</v>
+        <v>19</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>6.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.1</v>
+        <v>22.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>23.1</v>
+        <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>54.5</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>26.8</v>
+        <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>77.8</v>
+        <v>1.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>25.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3890,76 +3938,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
+      <c r="Y41" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="U41" s="3" t="n">
+      <c r="Z41" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>3.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3974,77 +4022,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>448.8</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+2 6
+</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>11.4</v>
+        <v>33.1</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>17.4</v>
+        <v>25.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>20.8</v>
+        <v>12.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>21.7</v>
+        <v>25.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>58.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>16.1</v>
+        <v>5.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.6</v>
+        <v>63.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4060,76 +4112,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>24.9</v>
+        <v>341.3</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>25.8</v>
+        <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>78.09999999999999</v>
+        <v>15.2</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>30.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>22.6</v>
+        <v>66.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>22.2</v>
+        <v>12.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>50</v>
+        <v>21.1</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>23</v>
+        <v>6.3</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>21.4</v>
+        <v>61.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>87</v>
+        <v>0.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4145,76 +4197,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>16.9</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2.2</v>
+        <v>82.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>3.3</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>22.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>92.3</v>
+        <v>3.2</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>4.6</v>
+        <v>73.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4229,73 +4281,79 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="10" t="n">
-        <v>23.9</v>
+        <v>22.2</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>19.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>21.4</v>
+        <v>77.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>4.9</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.6</v>
+        <v>165.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>41.4</v>
+        <v>26.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>19.8</v>
+        <v>1825.6</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>20.1</v>
+        <v>67.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>2.4</v>
+        <v>21.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>7.4</v>
+        <v>69</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.2</v>
+        <v>11.9</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>455.1</v>
+        <v>242.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>7.1</v>
+        <v>21.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>124.2</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4311,43 +4369,46 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>240.1</v>
+        <v>5.3</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>48</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>16.6</v>
+        <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>3.4</v>
+        <v>19.4</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>825.6</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 8
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>324.1</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4356,29 +4417,31 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>22.9</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
         <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="8" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF9933"/>
         <bgColor rgb="00FF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -156,9 +150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,75 +763,69 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1.3</v>
+        <v>9437.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.2</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>22.4</v>
+        <v>142.1</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K4" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>17.5</v>
+      <c r="N4" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>27.8</v>
+      <c r="S4" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>63.7</v>
+        <v>631.1</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -854,29 +839,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E5" s="12" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
+      <c r="F5" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>25.8</v>
@@ -885,46 +866,42 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>24.3</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.2</v>
+        <v>12.9</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="n">
-        <v>20.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>35</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,76 +917,74 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="D6" s="12" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>12</v>
+      <c r="M6" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>188.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>23.9</v>
+      <c r="R6" s="8" t="n">
+        <v>232.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>25.9</v>
+        <v>651.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>1608.9</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.1</v>
+        <v>185</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,76 +1000,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="N7" s="8" t="n">
+        <v>67.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>187.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q7" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>5.1</v>
+        <v>2022.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>2.8</v>
+      <c r="X7" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>5.2</v>
+        <v>177.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1110,61 +1083,61 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>86.2</v>
+        <v>1297.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.4</v>
+        <v>16.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="K8" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>865.6</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>82.7</v>
+        <v>187.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>2524.1</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
@@ -1172,14 +1145,14 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>22</v>
+      <c r="X8" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>96.2</v>
+        <v>90.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1195,24 +1168,20 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F9" s="11" t="n"/>
+        <v>1666.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>611.1</v>
+        <v>681.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>80.5</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
@@ -1220,49 +1189,43 @@
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>94.3</v>
+        <v>194.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>96.3</v>
+        <v>196.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>1440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>12.9</v>
+        <v>162.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>138.8</v>
+        <v>1138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>11.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.9</v>
+        <v>132.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>360.9</v>
+        <v>1360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1126.1</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1278,76 +1241,72 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.2</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1.6</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="L10" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M10" s="8" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>88.2</v>
+        <v>188.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>2.6</v>
+      <c r="S10" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2.2</v>
+        <v>272.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.4</v>
+        <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.8</v>
+        <v>0.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>806.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1363,77 +1322,73 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445.6</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>10.7</v>
+      <c r="N11" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>187.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>27.9</v>
+        <v>41.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>31.9</v>
+      <c r="S11" s="8" t="n">
+        <v>981.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="U11" s="8" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>197.5</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1450,32 +1405,32 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F12" s="12" t="n">
+      <c r="D12" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>84.5</v>
+        <v>18.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1487,10 +1442,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>72.2</v>
+        <v>27.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1499,25 +1454,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>8544.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X12" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,33 +1488,33 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>356.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F13" s="12" t="n">
+        <v>39356.7</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>12.6</v>
+      <c r="H13" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1569,40 +1524,38 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>189.1</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>24.7</v>
+      <c r="S13" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>44.4</v>
+        <v>197.7</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1618,43 +1571,41 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>340.8</v>
-      </c>
-      <c r="D14" s="12" t="n">
+        <v>13974</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>22.9</v>
+      <c r="E14" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.3</v>
@@ -1663,10 +1614,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1680,11 +1631,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1705,41 +1656,39 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>44.1</v>
+      <c r="D15" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1750,29 +1699,29 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="S15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>63.8</v>
+        <v>163.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>21.1</v>
+      <c r="V15" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>241.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>11.5</v>
+        <v>174</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1788,76 +1737,70 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>929.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
+        <v>11992.8</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>150.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>11.1</v>
-      </c>
+        <v>190.3</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>160.9</v>
+        <v>1100.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>21122.2</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>11.1</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>142.8</v>
+        <v>1142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.7</v>
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>42.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>368.7</v>
+        <v>1368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533.4</v>
+        <v>533441.5</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>45.1</v>
+        <v>1455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1872,79 +1815,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-3986
-</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
+      <c r="C17" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>14.4</v>
+      <c r="F17" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>18.1</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>1</v>
+      <c r="N17" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>28.6</v>
+      <c r="Q17" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>22.5</v>
+        <v>946.4</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>6.6</v>
+        <v>173.7</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>42.8</v>
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1.9</v>
+        <v>191</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1960,31 +1899,29 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>3.5</v>
+      <c r="E18" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>39.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.6</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
@@ -1996,44 +1933,40 @@
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>63.1</v>
+        <v>163.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-8 179
-</t>
-        </is>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2049,46 +1982,46 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>423.9</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>14.2</v>
+        <v>1423.9</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>124.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>28.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
+      <c r="M19" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87.5</v>
+        <v>2.3</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>31.8</v>
@@ -2100,33 +2033,25 @@
         <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
+        <v>62.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>85.8</v>
+      <c r="V19" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-44
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-818
-</t>
-        </is>
+      <c r="X19" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2142,80 +2067,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-1 8 4
-7
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>82.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="K20" s="8" t="n">
+        <v>2408</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>21.1</v>
+        <v>189</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>535.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.8</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>167.2</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2230,78 +2152,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="D21" s="12" t="n">
+        <v>1433.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>12.4</v>
+        <v>17.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.3</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>41.7</v>
+        <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>531</v>
+        <v>151</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>44.3</v>
+      <c r="V21" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-8111
-</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.1</v>
+        <v>185</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2317,46 +2233,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>84.5</v>
+        <v>374</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>24.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2</v>
+        <v>15.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.5</v>
+        <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>872</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>187</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2364,26 +2280,26 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>568.1</v>
+        <v>156.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>21.8</v>
+      <c r="V22" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>4.6</v>
+      <c r="X22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>185.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2402,19 +2318,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1985.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>653.4</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>123</v>
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>122.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.3</v>
+        <v>160.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2423,55 +2339,47 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
+        <v>135.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>95.2</v>
+        <v>195.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>882.6</v>
+        <v>1882.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>438.2</v>
+        <v>1437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>4.3</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2952.6</v>
+        <v>1295.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>10.7</v>
-      </c>
+        <v>85.2</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
       <c r="X23" s="3" t="n">
-        <v>26.7</v>
+        <v>1126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.4</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2487,22 +2395,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5851.1</v>
-      </c>
-      <c r="D24" s="12" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2510,23 +2418,21 @@
       <c r="J24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>1.3</v>
+      <c r="M24" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>872.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2536,25 +2442,25 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>4.4</v>
+        <v>17.6</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>0.9</v>
+      <c r="X24" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.8</v>
+        <v>182.2</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2570,19 +2476,19 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>45.1</v>
+        <v>1374</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.8</v>
@@ -2591,55 +2497,53 @@
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>13.6</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>60.4</v>
+        <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>324.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.8</v>
+        <v>243.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>56.9</v>
+        <v>956.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>66.09999999999999</v>
+      <c r="X25" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>74.8</v>
+        <v>1747.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2655,76 +2559,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>45.1</v>
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>36.3</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.1</v>
+        <v>1.6</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>60.4</v>
+        <v>949.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>324.3</v>
+        <v>24.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>56.9</v>
+        <v>180</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.8</v>
+        <v>181.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2740,80 +2644,74 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>381.2</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>24.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>2.6</v>
+        <v>17.8</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>19</v>
+        <v>5.3</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.2</v>
+        <v>187.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.9</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>168.4</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6.1</v>
+        <v>10.6</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>24.6</v>
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-54
-</t>
-        </is>
+        <v>180.8</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2829,76 +2727,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.2</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E28" s="12" t="n">
+        <v>9389.299999999999</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>61.2</v>
+      <c r="N28" s="8" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>82.5</v>
+        <v>187.4</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>63.5</v>
-      </c>
       <c r="W28" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>8.1</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,76 +2812,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E29" s="9" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>239.6</v>
-      </c>
       <c r="L29" s="3" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>28.2</v>
+        <v>21.3</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>24.8</v>
+      <c r="S29" s="8" t="n">
+        <v>226.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>162.6</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>26</v>
+        <v>14.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>27.6</v>
+        <v>23</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2999,76 +2897,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>494.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>24.9</v>
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.1</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.1</v>
+        <v>191.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>20.2</v>
+        <v>125.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>20.3</v>
+        <v>199.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.5</v>
+        <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>21.5</v>
+        <v>1103.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>90</v>
+        <v>1441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>28.6</v>
+        <v>1138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23</v>
+        <v>1113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>24.5</v>
+        <v>122.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>62.6</v>
+        <v>1332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.6</v>
+        <v>164.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.5</v>
+        <v>1823.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>23</v>
+        <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>26.5</v>
+        <v>1124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>1399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.6</v>
+        <v>32.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3084,76 +2982,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.1</v>
+        <v>383.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.9</v>
+        <v>184.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>25.4</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>93.2</v>
+        <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>113.6</v>
+        <v>6.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>44.4</v>
+        <v>188.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>38.5</v>
+        <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.7</v>
+        <v>22.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>18.7</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>334.8</v>
+        <v>166.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>24.3</v>
+        <v>22</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>322.8</v>
+        <v>80</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3171,78 +3067,70 @@
       <c r="C32" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="D32" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.2</v>
+        <v>14.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>18.5</v>
+        <v>12.3</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>188.4</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.7</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.5</v>
+        <v>156.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>42.9</v>
+        <v>23.7</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-78
-</t>
-        </is>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1118.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3258,76 +3146,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3272</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>26.5</v>
+        <v>1397</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>26.8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12.6</v>
+        <v>34.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>19.3</v>
+        <v>49.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>61.5</v>
+        <v>26.7</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>28.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>44</v>
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>25.4</v>
+        <v>63.4</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>1947.7</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>2.8</v>
+      <c r="W33" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>5.8</v>
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2.6</v>
+        <v>127.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3343,80 +3229,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>26.2</v>
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>13.9</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J34" s="3" t="n">
-        <v>5.5</v>
+        <v>12.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>187.3</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.2</v>
+        <v>17.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>45.5</v>
+        <v>55.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-5
-</t>
-        </is>
+        <v>183.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3432,52 +3312,54 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>884.5</v>
-      </c>
-      <c r="D35" s="12" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.4</v>
+        <v>23.9</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>24.1</v>
+        <v>10.4</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>61.3</v>
+      <c r="N35" s="8" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>25.4</v>
+        <v>854.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3492,14 +3374,14 @@
       <c r="W35" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3517,17 +3399,17 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>24.8</v>
+      <c r="E36" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>19</v>
@@ -3539,7 +3421,7 @@
         <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3547,23 +3429,23 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>21.2</v>
+      <c r="N36" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>25.8</v>
+      <c r="S36" s="8" t="n">
+        <v>593.8</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>72.3</v>
@@ -3571,18 +3453,20 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X36" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>326.6</v>
+        <v>178.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.4</v>
+        <v>16.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3598,22 +3482,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>35.5</v>
-      </c>
+        <v>11683.5</v>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>192.4</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3622,52 +3500,44 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>16.2</v>
+        <v>160.8</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>117.2</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>432.5</v>
+        <v>1432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>691.6</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>6.4</v>
+        <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>62.7</v>
+        <v>126.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.1</v>
+        <v>3431.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>651.5</v>
+        <v>165.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>79.3</v>
+        <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>62.9</v>
+        <v>342.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3685,74 +3555,72 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>25.1</v>
+      <c r="D38" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>82.5</v>
+      <c r="H38" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>7.4</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>44.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>87.5</v>
+        <v>187.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>17.9</v>
+        <v>27.9</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>68.7</v>
+        <v>168.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>52.6</v>
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>0.1</v>
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>35.4</v>
+        <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.1</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3768,15 +3636,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="D39" s="12" t="n">
+        <v>1400.8</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3786,58 +3654,58 @@
         <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>15.5</v>
+        <v>52.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>41.5</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="8" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>31.4</v>
+        <v>91</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>31.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>54.5</v>
+        <v>345.1</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+      <c r="X39" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>85.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3853,31 +3721,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>6.4</v>
+      <c r="I40" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3886,16 +3754,16 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>22.1</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7</v>
+        <v>18.7</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>19.8</v>
@@ -3904,7 +3772,7 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>89.7</v>
+        <v>189.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
@@ -3913,16 +3781,16 @@
         <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3938,40 +3806,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>24.5</v>
+        <v>1448.8</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>24.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.4</v>
+        <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.8</v>
+        <v>20.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>89.09999999999999</v>
@@ -3982,32 +3850,32 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>584.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>28.5</v>
+        <v>4.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0.1</v>
+        <v>174</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4022,81 +3890,77 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-2 6
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="C42" s="3" t="n">
+        <v>464.3</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.8</v>
+        <v>20.1</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>5.2</v>
+        <v>130</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>63.2</v>
+        <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>24.4</v>
+        <v>0.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4112,25 +3976,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>15.3</v>
+      <c r="F43" s="11" t="n">
+        <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.2</v>
+        <v>24.9</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>2.8</v>
@@ -4151,37 +4015,37 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>66.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.3</v>
+        <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.1</v>
+        <v>181.4</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>61.1</v>
+        <v>15.7</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>791.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4199,14 +4063,14 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>19.8</v>
+      <c r="D44" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>21.5</v>
+        <v>44.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4215,59 +4079,53 @@
         <v>18.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>82.8</v>
+        <v>10.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>20.1</v>
+        <v>6.5</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>89</v>
+        <v>390.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>3.3</v>
+        <v>12.4</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.2</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>33.5</v>
+        <v>15.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>73.8</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4281,79 +4139,59 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="C45" s="3" t="n">
+        <v>16871.1</v>
+      </c>
+      <c r="D45" s="10" t="inlineStr"/>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>13.3</v>
+        <v>123.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>165.6</v>
+        <v>116.6</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.6</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>67.7</v>
-      </c>
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>37.2</v>
+        <v>10234.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.4</v>
+        <v>1167.4</v>
       </c>
       <c r="Q45" s="3" t="n">
+        <v>1691.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="S45" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>22.9</v>
-      </c>
       <c r="T45" s="3" t="n">
-        <v>69</v>
+        <v>4084.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>242.4</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>21.8</v>
-      </c>
+        <v>112.2</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
+        <v>184832438.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4369,43 +4207,38 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E46" s="10" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>48</v>
+      <c r="F46" s="11" t="n">
+        <v>24</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>1.1</v>
+      <c r="H46" s="8" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>825.6</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20 8
-</t>
-        </is>
+      <c r="M46" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4413,36 +4246,34 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+      <c r="Q46" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="W46" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,14 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,62 +772,64 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9437.5</v>
+        <v>83.7</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>31.2</v>
+        <v>18.2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.4</v>
+        <v>17.2</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>14.4</v>
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>91241.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>82.5</v>
+        <v>178.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>631.1</v>
+        <v>63.7</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18.1</v>
+        <v>27.7</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -839,28 +850,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>21.5</v>
+      <c r="C5" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.8</v>
+        <v>9.6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -868,37 +879,41 @@
       <c r="M5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N5" s="8" t="n">
-        <v>19.9</v>
+      <c r="N5" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
-        <v>27.5</v>
+      <c r="W5" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>72.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>726.1</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -917,7 +932,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.4</v>
+        <v>831.6</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>31.4</v>
@@ -931,60 +946,62 @@
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>232.9</v>
+      <c r="R6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>651.1</v>
+        <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>1608.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1000,71 +1017,71 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1437.3</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.8</v>
+        <v>143.7</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="G7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>67.3</v>
+      <c r="N7" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>187.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2022.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="8" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="W7" s="3" t="inlineStr"/>
       <c r="X7" s="8" t="n">
-        <v>27.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>177.9</v>
+        <v>1772.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1083,15 +1100,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1297.2</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>98971.60000000001</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="E8" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1101,40 +1118,40 @@
         <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>187.7</v>
+        <v>87.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2524.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>11.6</v>
@@ -1145,15 +1162,13 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>90.2</v>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1168,64 +1183,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1666.5</v>
+        <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
+        <v>1152.6</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>122.9</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>681.1</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>211.2</v>
+      </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>196.3</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1440.9</v>
+        <v>1840.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>162.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1138.8</v>
+        <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>1217.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>132.9</v>
+        <v>1831.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1360.9</v>
+        <v>360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>126.1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>113</v>
+      </c>
       <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="n">
+        <v>11418.4</v>
+      </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>58.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1241,39 +1266,43 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>16.1</v>
+      <c r="H10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="8" t="n">
+        <v>19.3</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>188.2</v>
+        <v>88.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1281,29 +1310,29 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>272.2</v>
+        <v>72.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0.5</v>
+        <v>25.2</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>16.6</v>
@@ -1322,7 +1351,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445</v>
+        <v>1445.1</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>28.7</v>
@@ -1340,55 +1369,59 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>20.7</v>
+        <v>46.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>41.9</v>
+        <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>981.9</v>
+        <v>230.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V11" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>24.7</v>
+      <c r="W11" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>97.5</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1403,10 +1436,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.6</v>
+        <v>318.3</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>19.6</v>
@@ -1415,22 +1448,22 @@
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>18</v>
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1442,10 +1475,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>27.8</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1454,25 +1487,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>8544.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="X12" s="8" t="n">
+      <c r="W12" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>10.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1488,13 +1521,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>39356.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>25.5</v>
@@ -1502,19 +1535,19 @@
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>12.6</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1524,10 +1557,12 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1539,23 +1574,23 @@
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V13" s="8" t="n">
+      <c r="U13" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>197.7</v>
+        <v>192.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1571,13 +1606,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13974</v>
+        <v>32.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>26.1</v>
@@ -1586,29 +1621,31 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1617,7 +1654,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1654,13 +1691,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>433.5</v>
+        <v>1643.3</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>24.9</v>
@@ -1668,27 +1705,29 @@
       <c r="G15" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1699,26 +1738,26 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>163.8</v>
+        <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>241.1</v>
+      <c r="W15" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>174</v>
+        <v>1741</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1737,22 +1776,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11992.8</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>124.7</v>
+        <v>199.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1129.9</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>124.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>150.8</v>
+        <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.3</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
@@ -1762,42 +1801,46 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1100.9</v>
+        <v>460.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.2</v>
+        <v>1055.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.1</v>
+        <v>4464.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>102.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1142.8</v>
+        <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>123</v>
+        <v>1123</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1368.7</v>
+        <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533441.5</v>
+        <v>53.1</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>137.5</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1455.1</v>
+        <v>455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>13.4</v>
@@ -1816,7 +1859,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.9</v>
+        <v>5.8</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>30</v>
@@ -1827,51 +1870,47 @@
       <c r="F17" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>81.2</v>
+      <c r="I17" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>20</v>
+      <c r="N17" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>946.4</v>
+      <c r="Q17" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>23.7</v>
       </c>
       <c r="U17" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>24.2</v>
+        <v>48.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
@@ -1899,56 +1938,56 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>39.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>12.7</v>
+        <v>27.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>163.1</v>
+        <v>6.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
@@ -1956,11 +1995,11 @@
       <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>31</v>
+      <c r="X18" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1982,77 +2021,75 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1423.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>124.8</v>
+      <c r="G19" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.1</v>
+        <v>11.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>28.5</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.3</v>
+        <v>87.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>31.8</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>61.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>25.3</v>
+        <v>94.2</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>295.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>62.1</v>
+        <v>54</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>25.8</v>
+        <v>655.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.2</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2067,39 +2104,37 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E20" s="11" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>23.5</v>
+      <c r="F20" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>82.2</v>
+      <c r="H20" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2408</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2109,31 +2144,31 @@
         <v>12.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>19.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>167.2</v>
+        <v>67.2</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>10.2</v>
@@ -2152,7 +2187,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1433.5</v>
+        <v>43.3</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>30.8</v>
@@ -2167,29 +2202,33 @@
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.4</v>
+        <v>12.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="8" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2199,16 +2238,16 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
@@ -2233,28 +2272,26 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I22" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
@@ -2269,10 +2306,10 @@
         <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21.6</v>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2280,29 +2317,29 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>156.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19.5</v>
+      <c r="V22" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>93.5</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2320,17 +2357,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="9" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>122.9</v>
+      <c r="E23" s="9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>160.3</v>
+        <v>16027.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2339,44 +2376,52 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>135.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>195.2</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1882.8</v>
+        <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1437.2</v>
+        <v>1137.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>1535.7</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1145.1</v>
+      </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1295.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>210.7</v>
+      </c>
       <c r="X23" s="3" t="n">
-        <v>1126.7</v>
+        <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>1811</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2395,44 +2440,48 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E24" s="11" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>24.6</v>
+      <c r="F24" s="9" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>87.40000000000001</v>
+        <v>12.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>19.5</v>
+      <c r="N24" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="8" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2442,23 +2491,21 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="n">
-        <v>182.2</v>
-      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2476,74 +2523,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>32.1</v>
+        <v>21.5</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>25.7</v>
+        <v>20.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.1</v>
+        <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>81414.60000000001</v>
+      </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>243.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>956.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1747.6</v>
+        <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2559,7 +2608,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.8</v>
+        <v>329.2</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>30.8</v>
@@ -2573,32 +2622,32 @@
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>11.9</v>
+      <c r="H26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>949.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.4</v>
@@ -2610,23 +2659,21 @@
         <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V26" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="n">
-        <v>181.1</v>
-      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2644,16 +2691,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>952.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>23.8</v>
+      <c r="E27" s="10" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
@@ -2661,50 +2708,52 @@
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="8" t="n">
-        <v>21.9</v>
+      <c r="I27" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>23.2</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2727,31 +2776,31 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9389.299999999999</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="10" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.6</v>
@@ -2760,40 +2809,40 @@
         <v>19.2</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>21.3</v>
+        <v>281.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>164.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>23.6</v>
+        <v>55.6</v>
       </c>
       <c r="X28" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2812,16 +2861,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="D29" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.9</v>
+      <c r="E29" s="10" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.1</v>
@@ -2830,7 +2879,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2844,23 +2893,23 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
-        <v>226.5</v>
+      <c r="S29" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>162.6</v>
@@ -2868,17 +2917,17 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8182.8</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>16.1</v>
@@ -2897,22 +2946,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>124.1</v>
+        <v>11836.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1224.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.9</v>
+        <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>180</v>
@@ -2921,49 +2970,49 @@
         <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>125.4</v>
+        <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1103.2</v>
+        <v>9103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1441.9</v>
+        <v>14241.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1138.5</v>
+        <v>138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1113.7</v>
+        <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>122.8</v>
+        <v>122.7</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1332.8</v>
+        <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>164.5</v>
+        <v>16.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1823.1</v>
+        <v>1123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1124.3</v>
+        <v>164.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1399.8</v>
+        <v>39.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2982,22 +3031,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>24.8</v>
+      <c r="F31" s="9" t="n">
+        <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>184.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>182.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3005,52 +3054,52 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6.4</v>
+        <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>188.4</v>
+        <v>22.4</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q31" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
-        <v>24.5</v>
+      <c r="S31" s="3" t="n">
+        <v>845.8</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>166.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.5</v>
-      </c>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3065,72 +3114,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E32" s="11" t="n">
+        <v>943.7</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N32" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>188.4</v>
-      </c>
-      <c r="P32" s="3" t="inlineStr"/>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>156.6</v>
+        <v>560.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>128.8</v>
       </c>
       <c r="X32" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1118.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3146,38 +3199,40 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1397</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>26.8</v>
+        <v>397.1</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>65.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>34.1</v>
+        <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>1.1</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>49.5</v>
+        <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>87.40000000000001</v>
@@ -3185,32 +3240,32 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>63.4</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>1947.7</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>127.6</v>
+        <v>122.6</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>17.4</v>
@@ -3229,7 +3284,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>362.4</v>
+        <v>36.2</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>30.4</v>
@@ -3240,20 +3295,20 @@
       <c r="F34" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>4.2</v>
+      <c r="K34" s="8" t="n">
+        <v>2.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3265,26 +3320,28 @@
         <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>7886.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.2</v>
+        <v>7.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>55.4</v>
+        <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
@@ -3293,10 +3350,10 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>183.2</v>
+        <v>1832.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3324,64 +3381,64 @@
         <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>23.9</v>
+        <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="N35" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>854.1</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>188.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3400,13 +3457,13 @@
         <v>398.9</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>28.6</v>
+        <v>38.6</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>20</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>24.3</v>
+        <v>29.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>18.6</v>
@@ -3418,10 +3475,10 @@
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3429,45 +3486,43 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>593.8</v>
+      <c r="S36" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>72.3</v>
+        <v>822.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>5</v>
+        <v>95.8</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.8</v>
+        <v>46.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>16.9</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3484,14 +3539,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="10" t="inlineStr"/>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr"/>
+      <c r="D37" s="9" t="n">
+        <v>1450.1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>125.5</v>
+      </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>192.4</v>
+        <v>9224.1</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3500,44 +3561,52 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>160.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>1396.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>127.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>1432.5</v>
+        <v>437.5</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>139.6</v>
+        <v>129</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126.8</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3431.1</v>
+        <v>343.7</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>165.7</v>
+        <v>65.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>127.1</v>
+      </c>
       <c r="Y37" s="3" t="n">
         <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>342.4</v>
+        <v>34.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3555,28 +3624,30 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>5.4</v>
+      <c r="F38" s="11" t="n">
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.5</v>
+        <v>88.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -3584,13 +3655,13 @@
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>27.9</v>
@@ -3598,29 +3669,29 @@
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>25.2</v>
+      <c r="S38" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>168.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>22.4</v>
+        <v>224.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>79.3</v>
+        <v>179.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3636,76 +3707,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
+        <v>14001.8</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>12.3</v>
+        <v>25.7</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>52.5</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>3.9</v>
+        <v>29.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>22</v>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P39" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+      <c r="P39" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>345.1</v>
+        <v>534.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>27.6</v>
+      <c r="X39" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>175.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3723,29 +3792,29 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>20.2</v>
+      <c r="D40" s="10" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>90.2</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3753,16 +3822,16 @@
       <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>10.1</v>
+      <c r="N40" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3772,25 +3841,25 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>189.7</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19.6</v>
+        <v>28.3</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>21.7</v>
+        <v>217.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>85.5</v>
+        <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.7</v>
+        <v>19.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3806,33 +3875,33 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1448.8</v>
+        <v>114.8</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>19.6</v>
+        <v>49.43</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>24.4</v>
+        <v>34.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3850,26 +3919,26 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>584.5</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>4.6</v>
+        <v>24.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>174</v>
@@ -3891,7 +3960,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.3</v>
+        <v>86.2</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>32.8</v>
@@ -3902,32 +3971,32 @@
       <c r="F42" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>20.1</v>
+        <v>0.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>72.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>12.1</v>
@@ -3938,29 +4007,29 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>0.2</v>
+        <v>25.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>18708</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3976,7 +4045,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
+        <v>44.1</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>32</v>
@@ -3990,14 +4059,14 @@
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>24.9</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4015,37 +4084,35 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V43" s="8" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>791.4</v>
+      <c r="W43" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4061,16 +4128,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D44" s="8" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D44" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>44.5</v>
+      <c r="E44" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>21.4</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4078,8 +4145,8 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>10.8</v>
+      <c r="I44" s="8" t="n">
+        <v>80.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
@@ -4091,34 +4158,34 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>6.5</v>
+        <v>19.9</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>390.1</v>
+        <v>189</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q44" s="8" t="n">
-        <v>28.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181</v>
+        <v>181.9</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>822.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>20.2</v>
@@ -4140,52 +4207,66 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16871.1</v>
-      </c>
-      <c r="D45" s="10" t="inlineStr"/>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+        <v>18841.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>174</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>105.6</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>123.3</v>
+        <v>169</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>30</v>
+        <v>2816.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>12180.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>110109210619.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>10234.2</v>
+        <v>204.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1167.4</v>
+        <v>16808.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1691.2</v>
+        <v>1257.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>129.7</v>
+        <v>1291.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>26.2</v>
+        <v>18317.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>4084.4</v>
+        <v>44841.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>112.2</v>
+        <v>81.5</v>
       </c>
       <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="n">
+        <v>1122.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>184832438.2</v>
+        <v>924.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
@@ -4207,7 +4288,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
+        <v>511.7</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>29.1</v>
@@ -4218,19 +4299,21 @@
       <c r="F46" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>2.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>122.6</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4238,7 +4321,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>20.2</v>
+        <v>60.5</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4246,33 +4329,31 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="8" t="n">
+      <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>81.5</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,13 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,20 +768,20 @@
       <c r="C4" s="3" t="n">
         <v>83.7</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91241.10000000001</v>
+        <v>91124.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -796,16 +790,16 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>17.6</v>
+        <v>88.8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>178.5</v>
+      <c r="N4" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -829,7 +823,7 @@
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -853,26 +847,24 @@
       <c r="C5" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>13.5</v>
+      <c r="F5" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -880,14 +872,12 @@
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
@@ -901,19 +891,19 @@
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>72.5</v>
+      <c r="X5" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>726.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -932,31 +922,31 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>831.6</v>
-      </c>
-      <c r="D6" s="11" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -983,10 +973,10 @@
         <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>26.2</v>
@@ -1017,25 +1007,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>14.8</v>
+        <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
@@ -1043,17 +1033,17 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="M7" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1081,7 +1071,7 @@
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1772.9</v>
+        <v>727.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1100,15 +1090,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98971.60000000001</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="E8" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1130,7 +1120,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1186,12 +1176,12 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1152.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>122.9</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1201,7 +1191,7 @@
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>211.2</v>
+        <v>22.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1219,7 +1209,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1840.9</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1228,10 +1218,10 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1217.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1831.9</v>
+        <v>1231.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1245,12 +1235,14 @@
       <c r="W9" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="X9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>11418.4</v>
+        <v>114102.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>58.8</v>
+        <v>38.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1268,30 +1260,26 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>15.2</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1302,7 +1290,7 @@
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1328,14 +1316,14 @@
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1351,31 +1339,31 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445.1</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>2445.1</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>18.2</v>
+      <c r="H11" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.1</v>
@@ -1383,35 +1371,35 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>46.7</v>
+      <c r="N11" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>230.8</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>5.7</v>
+        <v>58.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>4.1</v>
+        <v>2471.6</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1420,7 +1408,7 @@
         <v>97.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1436,22 +1424,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>318.3</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E12" s="11" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="H12" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1460,7 +1448,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>20.6</v>
@@ -1502,10 +1490,10 @@
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1521,15 +1509,15 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F13" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1542,10 +1530,10 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1583,11 +1571,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>192.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1608,27 +1596,25 @@
       <c r="C14" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F14" s="11" t="n">
+      <c r="D14" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
@@ -1636,7 +1622,7 @@
         <v>19.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>28.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1645,7 +1631,7 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1654,7 +1640,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1668,11 +1654,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1691,31 +1677,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1643.3</v>
-      </c>
-      <c r="D15" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>19.8</v>
+        <v>89.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>16.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
@@ -1745,7 +1731,7 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>24.5</v>
@@ -1757,7 +1743,7 @@
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1741</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1778,14 +1764,14 @@
       <c r="C16" s="3" t="n">
         <v>199.2</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>1129.9</v>
+      <c r="D16" s="11" t="n">
+        <v>19249.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>991.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>124.2</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>50.8</v>
@@ -1793,7 +1779,9 @@
       <c r="H16" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
@@ -1801,25 +1789,25 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>460.9</v>
+        <v>11.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1055.9</v>
+        <v>105.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4464.1</v>
+        <v>444.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>102.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1123</v>
+        <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
@@ -1859,29 +1847,33 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D17" s="11" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1889,7 +1881,7 @@
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
@@ -1898,31 +1890,31 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>82</v>
+        <v>8224</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>48.2</v>
+      <c r="V17" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1938,32 +1930,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>27.7</v>
@@ -1972,10 +1966,10 @@
         <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1987,19 +1981,19 @@
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>11.3</v>
+      <c r="W18" s="8" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -2021,19 +2015,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E19" s="3" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>18.4</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>11.6</v>
@@ -2042,7 +2036,7 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>91.5</v>
@@ -2062,14 +2056,14 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>61.8</v>
+      <c r="Q19" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>295.3</v>
+        <v>24.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>54</v>
@@ -2077,8 +2071,8 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>655.8</v>
+      <c r="V19" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
@@ -2087,7 +2081,7 @@
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2104,30 +2098,30 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>856.8</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>956.8</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>25.5</v>
+      <c r="F20" s="9" t="n">
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
@@ -2138,22 +2132,22 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>707.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
@@ -2162,7 +2156,7 @@
         <v>24.9</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>20.5</v>
+        <v>106.1</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2189,13 +2183,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2211,7 +2205,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2240,8 +2234,8 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>20.9</v>
+      <c r="U21" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.3</v>
@@ -2253,7 +2247,7 @@
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>185</v>
+        <v>850.8</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2272,23 +2266,25 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34.4</v>
+        <v>374.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="inlineStr"/>
+      <c r="E22" s="12" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>14.6</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>21.1</v>
+      <c r="I22" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
@@ -2327,19 +2323,19 @@
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="X22" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2357,17 +2353,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="9" t="n">
+      <c r="D23" s="11" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16027.4</v>
+        <v>605.9</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2379,7 +2375,7 @@
         <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>495.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2391,16 +2387,16 @@
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1137.2</v>
+        <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1535.7</v>
+        <v>113.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.2</v>
+        <v>14.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1145.1</v>
+        <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
@@ -2412,16 +2408,16 @@
         <v>85.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.2</v>
+        <v>22.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>210.7</v>
+        <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1811</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2440,28 +2436,28 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E24" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>84.59999999999999</v>
+      <c r="F24" s="11" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0.1</v>
@@ -2473,16 +2469,16 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>29.2</v>
+        <v>2.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>22.9</v>
@@ -2525,20 +2521,20 @@
       <c r="C25" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>20.7</v>
+      <c r="D25" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
@@ -2547,7 +2543,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>81414.60000000001</v>
+        <v>1.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2559,40 +2555,40 @@
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>4</v>
+        <v>31.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2610,13 +2606,13 @@
       <c r="C26" s="3" t="n">
         <v>329.2</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2628,8 +2624,8 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>12.6</v>
+      <c r="J26" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
@@ -2641,7 +2637,7 @@
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>19.2</v>
+        <v>89.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2656,13 +2652,13 @@
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2691,25 +2687,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>952.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="10" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>25.8</v>
+      <c r="E27" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2727,7 +2723,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2736,7 +2732,7 @@
         <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
@@ -2744,20 +2740,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>0.6</v>
+      <c r="U27" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>63.4</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>180.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2776,25 +2772,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="D28" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D28" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="10" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="E28" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2808,14 +2804,14 @@
       <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>281.3</v>
+      <c r="N28" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
@@ -2830,19 +2826,19 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="X28" s="8" t="n">
+        <v>956.1</v>
+      </c>
+      <c r="X28" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2861,19 +2857,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>50.31</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2894,13 +2890,13 @@
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2908,11 +2904,11 @@
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>162.6</v>
+        <v>62.4</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
@@ -2923,14 +2919,14 @@
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>8182.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2946,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11836.4</v>
+        <v>11856.4</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>150.5</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.8</v>
+        <v>97.8</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1224.1</v>
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>52.5</v>
@@ -2964,7 +2960,7 @@
         <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>15.8</v>
@@ -2973,22 +2969,22 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>929.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9103.4</v>
+        <v>103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14241.9</v>
+        <v>441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>138.5</v>
+        <v>238.5</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>113.7</v>
@@ -3000,19 +2996,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1123.1</v>
+        <v>123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>164.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>39.4</v>
+        <v>43.9</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -3031,22 +3027,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F31" s="9" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>182.4</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3054,10 +3050,8 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="8" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
@@ -3067,10 +3061,10 @@
         <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.7</v>
@@ -3079,25 +3073,25 @@
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>845.8</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>824.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3114,16 +3108,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>943.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>26.9</v>
+      <c r="F32" s="9" t="n">
+        <v>28.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>12.6</v>
@@ -3132,13 +3126,13 @@
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
@@ -3147,13 +3141,13 @@
         <v>19.3</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
@@ -3165,25 +3159,25 @@
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>560.6</v>
+        <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="V32" s="8" t="n">
-        <v>68.2</v>
+      <c r="V32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="X32" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>11.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3199,31 +3193,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>65.7</v>
+      <c r="F33" s="9" t="n">
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>1.1</v>
+      <c r="K33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
@@ -3243,8 +3237,8 @@
       <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>29.9</v>
+      <c r="R33" s="8" t="n">
+        <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
@@ -3265,10 +3259,10 @@
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>122.6</v>
+        <v>1727.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3286,16 +3280,16 @@
       <c r="C34" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3307,8 +3301,8 @@
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <v>2.4</v>
+      <c r="K34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3329,28 +3323,28 @@
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>7886.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>1832.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3369,15 +3363,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3402,10 +3396,10 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.3</v>
+        <v>29.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.6</v>
@@ -3423,22 +3417,22 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.1</v>
+        <v>28.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3456,20 +3450,20 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="E36" s="11" t="n">
+      <c r="D36" s="9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>29.3</v>
+      <c r="F36" s="9" t="n">
+        <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>190.1</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
@@ -3478,7 +3472,7 @@
         <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3487,7 +3481,7 @@
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3505,19 +3499,19 @@
         <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>822.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W36" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>46.8</v>
+      <c r="X36" s="3" t="n">
+        <v>84.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
@@ -3539,20 +3533,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1450.1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>125.5</v>
+      <c r="D37" s="11" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>92.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>9224.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3567,10 +3561,10 @@
         <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1396.5</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>127.2</v>
+        <v>18.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3579,13 +3573,13 @@
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>129</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126</v>
+        <v>1256</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3624,29 +3618,29 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>88.5</v>
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>18.4</v>
+        <v>0.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3670,25 +3664,25 @@
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>224.2</v>
+        <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>179.3</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>16.9</v>
@@ -3707,56 +3701,56 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14001.8</v>
-      </c>
-      <c r="D39" s="11" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>25.7</v>
+      <c r="E39" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>25.6</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>18.1</v>
+        <v>58.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>29.9</v>
+        <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>10.5</v>
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>12.8</v>
+      <c r="N39" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>534.5</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
@@ -3768,13 +3762,13 @@
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>175.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3792,20 +3786,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="E40" s="10" t="n">
+      <c r="D40" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <v>90.2</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3846,20 +3840,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>217.2</v>
+      <c r="V40" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>19.9</v>
+        <v>15.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3875,31 +3869,31 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="E41" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>34.5</v>
+      <c r="F41" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>11.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3938,10 +3932,10 @@
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>19.6</v>
@@ -3960,15 +3954,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>1464.5</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -3981,7 +3975,7 @@
         <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0.2</v>
@@ -4007,14 +4001,14 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>22.2</v>
+      <c r="S42" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="U42" s="8" t="n">
-        <v>28.2</v>
+      <c r="U42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
@@ -4022,11 +4016,11 @@
       <c r="W42" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>10.4</v>
+      <c r="X42" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>18708</v>
+        <v>182</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4045,15 +4039,15 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4066,7 +4060,7 @@
         <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4084,7 +4078,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4098,7 +4092,9 @@
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="U43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
@@ -4106,7 +4102,7 @@
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
@@ -4128,15 +4124,15 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="D44" s="11" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D44" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4145,11 +4141,11 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>80.8</v>
+      <c r="I44" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
@@ -4157,39 +4153,37 @@
       <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>0.8</v>
+      <c r="M44" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>189</v>
+        <v>890.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4207,72 +4201,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>18841.1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>841.1</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>174</v>
+        <v>168211.1</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>825.1</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>51.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>160.2</v>
+        <v>10.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>105.6</v>
+        <v>2637</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>169</v>
+        <v>183.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2816.1</v>
+        <v>28</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>12180.4</v>
+        <v>1910.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>110109210619.1</v>
+        <v>10092105.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>204.1</v>
+        <v>34.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16808.4</v>
+        <v>140.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1257.2</v>
+        <v>257.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1291.7</v>
+        <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18317.9</v>
+        <v>1382</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>44841.4</v>
+        <v>484</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="W45" s="3" t="n">
-        <v>1122.2</v>
+        <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>924.7</v>
+        <v>24.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4288,31 +4284,31 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>511.7</v>
-      </c>
-      <c r="D46" s="11" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>20.1</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>122.6</v>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4321,7 +4317,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>60.5</v>
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4330,7 +4326,7 @@
         <v>2.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>21.6</v>
@@ -4347,10 +4343,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
+      <c r="W46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -150,6 +162,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -792,7 +813,7 @@
       <c r="K4" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="15" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -810,7 +831,7 @@
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -822,7 +843,7 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -864,7 +885,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -881,7 +902,7 @@
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -893,7 +914,7 @@
       <c r="U5" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -966,7 +987,7 @@
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -978,7 +999,7 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="9" t="n">
         <v>26.2</v>
       </c>
       <c r="W6" s="3" t="n">
@@ -1021,7 +1042,7 @@
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="13" t="n">
         <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1036,10 +1057,10 @@
       <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="13" t="n">
         <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1051,7 +1072,7 @@
       <c r="Q7" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1063,11 +1084,11 @@
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="8" t="n">
+      <c r="W7" s="12" t="inlineStr"/>
+      <c r="X7" s="13" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
@@ -1134,7 +1155,7 @@
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1146,7 +1167,7 @@
       <c r="U8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1196,13 +1217,13 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="11" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="11" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1214,10 +1235,10 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="11" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1229,10 +1250,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="11" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="11" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1280,13 +1301,13 @@
         <v>6.2</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="11" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="13" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1295,10 +1316,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1310,10 +1331,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1353,7 +1374,7 @@
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
@@ -1380,7 +1401,7 @@
       <c r="P11" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1395,11 +1416,11 @@
       <c r="U11" s="3" t="n">
         <v>58.7</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>2471.6</v>
+      <c r="W11" s="15" t="n">
+        <v>247.16</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1465,7 +1486,7 @@
       <c r="P12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1480,7 +1501,7 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1550,7 +1571,7 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1565,7 +1586,7 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1633,7 +1654,7 @@
       <c r="P14" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1648,7 +1669,7 @@
       <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1718,7 +1739,7 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>28.5</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1733,7 +1754,7 @@
       <c r="U15" s="3" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1785,13 +1806,13 @@
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="11" t="n">
         <v>11.2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="11" t="n">
         <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1803,10 +1824,10 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="11" t="n">
         <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1818,10 +1839,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="11" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1871,10 +1892,10 @@
         <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1886,13 +1907,13 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="11" t="n">
         <v>8224</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1901,10 +1922,10 @@
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1932,7 +1953,7 @@
       <c r="C18" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="15" t="n">
         <v>40.8</v>
       </c>
       <c r="E18" s="3" t="n">
@@ -1956,7 +1977,7 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -1974,7 +1995,7 @@
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1986,10 +2007,10 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="15" t="n">
         <v>50.6</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2041,7 +2062,7 @@
       <c r="K19" s="3" t="n">
         <v>91.5</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2059,7 +2080,7 @@
       <c r="Q19" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2071,7 +2092,7 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2122,7 +2143,7 @@
       <c r="K20" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2137,10 +2158,10 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2152,11 +2173,11 @@
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>106.1</v>
+      <c r="W20" s="15" t="n">
+        <v>10.61</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2207,7 +2228,7 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2225,7 +2246,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2234,10 +2255,10 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="8" t="n">
+      <c r="U21" s="13" t="n">
         <v>8.9</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2271,13 +2292,13 @@
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="13" t="n">
         <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2292,7 +2313,7 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2310,7 +2331,7 @@
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2322,7 +2343,7 @@
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2374,13 +2395,13 @@
       <c r="J23" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>495.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="11" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2392,10 +2413,10 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>14.6</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="11" t="n">
         <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2407,10 +2428,10 @@
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="11" t="n">
         <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2462,10 +2483,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2477,10 +2498,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="11" t="n">
         <v>2.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2492,10 +2513,10 @@
       <c r="U24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2545,10 +2566,10 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2560,10 +2581,10 @@
       <c r="P25" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="9" t="n">
         <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2624,16 +2645,16 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="13" t="n">
         <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2645,10 +2666,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2701,7 +2722,7 @@
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="13" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
@@ -2713,10 +2734,10 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2728,10 +2749,10 @@
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2743,7 +2764,7 @@
       <c r="U27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="15" t="n">
         <v>63.4</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2798,10 +2819,10 @@
       <c r="K28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2813,10 +2834,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2831,8 +2852,8 @@
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>956.1</v>
+      <c r="W28" s="15" t="n">
+        <v>95.61</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2859,10 +2880,10 @@
       <c r="C29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="15" t="n">
         <v>49.4</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="15" t="n">
         <v>61.31</v>
       </c>
       <c r="F29" s="9" t="n">
@@ -2883,10 +2904,10 @@
       <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2898,13 +2919,13 @@
       <c r="P29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="13" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2965,13 +2986,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="11" t="n">
         <v>929.6</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2983,10 +3004,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="11" t="n">
         <v>238.5</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="11" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2998,10 +3019,10 @@
       <c r="U30" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="11" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="11" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3041,7 +3062,7 @@
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="13" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3051,10 +3072,10 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3066,10 +3087,10 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3081,10 +3102,10 @@
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="11" t="n">
         <v>824.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="11" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3134,13 +3155,13 @@
       <c r="K32" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3149,7 +3170,7 @@
       <c r="P32" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="9" t="n">
         <v>31</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3167,7 +3188,7 @@
       <c r="V32" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="13" t="n">
         <v>23.4</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3219,10 +3240,10 @@
       <c r="K33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3234,10 +3255,10 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="13" t="n">
         <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3304,10 +3325,10 @@
       <c r="K34" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3319,7 +3340,7 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3334,7 +3355,7 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="13" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3389,10 +3410,10 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3404,7 +3425,7 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3474,10 +3495,10 @@
       <c r="K36" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3489,7 +3510,7 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="9" t="n">
         <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3504,7 +3525,7 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="15" t="n">
         <v>58</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3554,13 +3575,13 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="11" t="n">
         <v>10.2</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3572,10 +3593,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="11" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3587,10 +3608,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="11" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="11" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3642,10 +3663,10 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3657,10 +3678,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3672,10 +3693,10 @@
       <c r="U38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3712,10 +3733,10 @@
       <c r="F39" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="13" t="n">
         <v>58.5</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="13" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
@@ -3725,13 +3746,13 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="13" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3740,10 +3761,10 @@
       <c r="P39" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="15" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3789,7 +3810,7 @@
       <c r="D40" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="15" t="n">
         <v>90.2</v>
       </c>
       <c r="F40" s="9" t="n">
@@ -3798,7 +3819,7 @@
       <c r="G40" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="13" t="n">
         <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3810,7 +3831,7 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3828,7 +3849,7 @@
       <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3840,7 +3861,7 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3895,7 +3916,7 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3913,7 +3934,7 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3931,7 +3952,7 @@
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
@@ -3980,7 +4001,7 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3998,10 +4019,10 @@
       <c r="Q42" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="13" t="n">
         <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
@@ -4065,7 +4086,7 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4083,7 +4104,7 @@
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4150,10 +4171,10 @@
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="8" t="n">
+      <c r="M44" s="13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4168,7 +4189,7 @@
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4183,7 +4204,7 @@
       <c r="V44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4224,13 +4245,13 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="11" t="n">
         <v>1910.4</v>
       </c>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="3" t="n">
         <v>10092105.9</v>
       </c>
@@ -4240,10 +4261,10 @@
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="11" t="n">
         <v>257.5</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="11" t="n">
         <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4255,10 +4276,10 @@
       <c r="U45" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="11" t="n">
         <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4298,7 +4319,7 @@
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="13" t="n">
         <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
@@ -4310,7 +4331,7 @@
       <c r="K46" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M46" s="3" t="n">
@@ -4325,10 +4346,10 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4340,10 +4361,10 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>21.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -158,13 +158,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,22 +793,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="D4" s="9" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91124.10000000001</v>
+        <v>27.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -811,12 +817,12 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="L4" s="15" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M4" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -828,10 +834,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -843,10 +849,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="V4" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W4" s="10" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -866,30 +872,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F5" s="9" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -898,26 +908,28 @@
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="P5" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="15" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V5" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -943,15 +955,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.6</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -961,18 +973,18 @@
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K6" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -984,10 +996,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -997,12 +1009,12 @@
         <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1030,72 +1042,74 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>84.8</v>
+      <c r="H7" s="15" t="n">
+        <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>27.3</v>
+        <v>10</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N7" s="15" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>872.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R7" s="9" t="n">
+      <c r="Q7" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>152.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X7" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>727.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1111,18 +1125,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.6</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="15" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1137,11 +1151,11 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.5</v>
+      <c r="M8" s="10" t="n">
+        <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1152,10 +1166,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1165,21 +1179,23 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V8" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V8" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1197,33 +1213,33 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>152.6</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>122.9</v>
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>822.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>22.2</v>
+        <v>11.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="9" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="10" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1235,14 +1251,14 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="10" t="n">
         <v>138.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>117.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1231.9</v>
+        <v>131.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1250,20 +1266,20 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="10" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="10" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>12.9</v>
+        <v>129.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>114102.4</v>
+        <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>38.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1281,33 +1297,37 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="9" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="13" t="n">
+      <c r="N10" s="15" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1316,10 +1336,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1331,10 +1351,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1360,70 +1380,70 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2445.1</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>85.2</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.7</v>
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q11" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q11" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="10" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>31.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
+        <v>850.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="15" t="n">
-        <v>247.16</v>
+      <c r="W11" s="10" t="n">
+        <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>31.9</v>
+        <v>502.1</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>97.5</v>
@@ -1445,22 +1465,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.3</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1469,9 +1489,9 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -1484,12 +1504,12 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q12" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="10" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1501,17 +1521,17 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="15" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>1197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1530,15 +1550,15 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D13" s="9" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1556,7 +1576,7 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1571,10 +1591,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1586,10 +1606,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1599,7 +1619,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1615,35 +1635,37 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>28.7</v>
+      <c r="M14" s="15" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1652,12 +1674,12 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1666,16 +1688,16 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="15" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1698,22 +1720,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="9" t="n">
+      <c r="E15" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89.8</v>
+        <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
@@ -1722,13 +1744,13 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>19.1</v>
+      <c r="M15" s="15" t="n">
+        <v>29.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1739,10 +1761,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1752,22 +1774,22 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="V15" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V15" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="15" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1783,55 +1805,53 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>19249.9</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="F16" s="11" t="n">
+        <v>1992.8</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="11" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>924.6</v>
+        <v>115.8</v>
+      </c>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.8</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.8</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="10" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="11" t="n">
-        <v>23</v>
+      <c r="R16" s="10" t="n">
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.5</v>
+        <v>1042.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1839,14 +1859,14 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="10" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="11" t="n">
+      <c r="W16" s="10" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>137.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>455.1</v>
@@ -1868,65 +1888,67 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>28.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M17" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>11551.5</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M17" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="11" t="n">
-        <v>8224</v>
-      </c>
-      <c r="S17" s="13" t="n">
+      <c r="R17" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>173.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="11" t="n">
-        <v>28</v>
+      <c r="W17" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
@@ -1951,70 +1973,70 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E18" s="3" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>14.9</v>
+      <c r="F18" s="10" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>14.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>24.9</v>
+        <v>13.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
-        <v>19.6</v>
+      <c r="L18" s="10" t="n">
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>27.7</v>
+        <v>20.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.9</v>
+        <v>13.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1.2</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="15" t="n">
-        <v>50.6</v>
+      <c r="W18" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -2036,16 +2058,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>433.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>25.4</v>
+        <v>2223.4</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>18.4</v>
@@ -2057,16 +2079,16 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="L19" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>28.2</v>
+      <c r="M19" s="15" t="n">
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
@@ -2077,10 +2099,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R19" s="9" t="n">
+      <c r="Q19" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2092,10 +2114,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2104,7 +2126,9 @@
       <c r="Y19" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2119,19 +2143,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>956.8</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1.8</v>
@@ -2139,11 +2163,13 @@
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="L20" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2153,31 +2179,31 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>21.5</v>
+      <c r="Q20" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R20" s="17" t="n">
+        <v>24.15</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>707.2</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="V20" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V20" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="15" t="n">
-        <v>10.61</v>
+      <c r="W20" s="10" t="n">
+        <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2204,13 +2230,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2228,11 +2254,11 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.3</v>
+        <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2241,34 +2267,34 @@
         <v>86.7</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q21" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="U21" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V21" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.8</v>
+        <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2287,19 +2313,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374.1</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>2374.6</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>84.59999999999999</v>
+      <c r="E22" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
@@ -2313,11 +2339,11 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>16.2</v>
+      <c r="M22" s="15" t="n">
+        <v>26.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2328,25 +2354,25 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>256.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="W22" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2372,19 +2398,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="E23" s="11" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="10" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>605.9</v>
+        <v>60.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2393,15 +2419,15 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>495.3</v>
-      </c>
-      <c r="L23" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" s="9" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2413,35 +2439,35 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R23" s="11" t="n">
-        <v>1143.1</v>
+      <c r="Q23" s="10" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>295.2</v>
+        <v>2895.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="V23" s="11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>21</v>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>226.7</v>
+        <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2457,22 +2483,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>1398.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>82.59999999999999</v>
+      <c r="F24" s="10" t="n">
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.7</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2483,14 +2509,14 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2498,8 +2524,8 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="11" t="n">
-        <v>2.9</v>
+      <c r="Q24" s="10" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>22.9</v>
@@ -2511,18 +2537,20 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V24" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="V24" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="n">
+        <v>82.2</v>
+      </c>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2540,15 +2568,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D25" s="9" t="n">
+        <v>2374</v>
+      </c>
+      <c r="D25" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2558,7 +2586,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.6</v>
@@ -2566,50 +2594,50 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>24</v>
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>25.9</v>
+        <v>22.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V25" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="15" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>17.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2625,40 +2653,40 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.2</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="13" t="n">
-        <v>25.6</v>
+      <c r="J26" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>89.2</v>
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2666,31 +2694,33 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="15" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2708,25 +2738,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>354.8</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>1354.4</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2734,25 +2764,25 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2761,20 +2791,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V27" s="15" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="U27" s="15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>84.8</v>
+        <v>802.1</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2793,15 +2823,15 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2817,12 +2847,12 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L28" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L28" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="10" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2834,10 +2864,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="10" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2847,13 +2877,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="15" t="n">
-        <v>95.61</v>
+      <c r="W28" s="10" t="n">
+        <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2862,7 +2892,7 @@
         <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2880,64 +2910,64 @@
       <c r="C29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="D29" s="15" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>61.31</v>
-      </c>
-      <c r="F29" s="9" t="n">
+      <c r="D29" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L29" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="15" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="13" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2963,22 +2993,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11856.4</v>
+        <v>1856.4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>150.5</v>
+        <v>150.3</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.5</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9.1</v>
+        <v>191.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2986,17 +3016,17 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="11" t="n">
-        <v>929.6</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="10" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="M30" s="10" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>441.9</v>
@@ -3004,10 +3034,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="11" t="n">
-        <v>238.5</v>
-      </c>
-      <c r="R30" s="11" t="n">
+      <c r="Q30" s="10" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="R30" s="10" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3017,19 +3047,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V30" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V30" s="10" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="10" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>61.3</v>
+        <v>124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>43.9</v>
+        <v>399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -3048,34 +3078,36 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>94.8</v>
+        <v>37.1</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="15" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3087,34 +3119,36 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="11" t="n">
-        <v>824.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W31" s="10" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3129,51 +3163,51 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G32" s="15" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="13" t="n">
-        <v>28.5</v>
+      <c r="N32" s="15" t="n">
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="10" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3183,22 +3217,22 @@
         <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V32" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="13" t="n">
-        <v>23.4</v>
+      <c r="W32" s="10" t="n">
+        <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>169.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3214,16 +3248,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="D33" s="9" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="D33" s="10" t="n">
         <v>33.6</v>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>26.7</v>
+      <c r="E33" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>26.8</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>13.9</v>
@@ -3238,12 +3272,12 @@
         <v>5.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3255,35 +3289,35 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="10" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="13" t="n">
-        <v>38.9</v>
+      <c r="R33" s="10" t="n">
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>47.7</v>
+        <v>147.7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V33" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1727.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>7.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3299,36 +3333,36 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="D34" s="9" t="n">
+        <v>1362.4</v>
+      </c>
+      <c r="D34" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L34" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="10" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3340,10 +3374,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3355,17 +3389,17 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="13" t="n">
+      <c r="V34" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3386,20 +3420,20 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0.3</v>
@@ -3410,14 +3444,14 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="L35" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="10" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>29.3</v>
+        <v>20</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3425,10 +3459,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3438,12 +3472,12 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="W35" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V35" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W35" s="10" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3471,38 +3505,38 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>190.1</v>
+      <c r="H36" s="15" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3510,10 +3544,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3525,19 +3559,21 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="W36" s="3" t="n">
+      <c r="V36" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W36" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3552,19 +3588,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>11683.5</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>92.5</v>
+      <c r="E37" s="10" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>49.2</v>
+        <v>149.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3575,17 +3611,17 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>10.2</v>
+      <c r="K37" s="9" t="n">
+        <v>102.8</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.7</v>
+        <v>107.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3593,14 +3629,14 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="10" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="10" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1256</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3608,10 +3644,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="10" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="11" t="n">
+      <c r="W37" s="10" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3637,15 +3673,15 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>2326.7</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3658,19 +3694,19 @@
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>28.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>87.5</v>
@@ -3678,26 +3714,26 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="V38" s="11" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="V38" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="11" t="n">
-        <v>224.1</v>
+      <c r="W38" s="10" t="n">
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
@@ -3706,7 +3742,7 @@
         <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3722,53 +3758,55 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>1400.8</v>
+      </c>
+      <c r="D39" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="G39" s="13" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H39" s="13" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J39" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="13" t="n">
-        <v>88.40000000000001</v>
+      <c r="N39" s="15" t="n">
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q39" s="15" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="R39" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R39" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>54.5</v>
@@ -3776,10 +3814,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3807,20 +3845,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D40" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="13" t="n">
-        <v>89</v>
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>129</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3831,14 +3869,14 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>22.2</v>
+        <v>24.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3846,10 +3884,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3861,20 +3899,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="13" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19</v>
+      <c r="V40" s="10" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W40" s="10" t="n">
+        <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>181.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>15.9</v>
+        <v>81.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3890,15 +3928,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F41" s="9" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3908,7 +3946,7 @@
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
@@ -3916,10 +3954,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="10" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3931,10 +3969,10 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3946,20 +3984,20 @@
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="13" t="n">
+      <c r="X41" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3975,18 +4013,18 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1464.5</v>
-      </c>
-      <c r="D42" s="9" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="D42" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="15" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4001,10 +4039,10 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M42" s="3" t="n">
+      <c r="L42" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4014,37 +4052,37 @@
         <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q42" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="13" t="n">
-        <v>28.2</v>
+      <c r="S42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>25.8</v>
+      <c r="W42" s="10" t="n">
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>182</v>
+        <v>24.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>87</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4060,18 +4098,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="15" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4086,47 +4124,47 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="15" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>188.1</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="3" t="n">
+      <c r="S43" s="15" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V43" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V43" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>53.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>14.6</v>
@@ -4147,13 +4185,13 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4166,45 +4204,47 @@
         <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>20.1</v>
+      <c r="M44" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N44" s="15" t="n">
+        <v>4.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>890.1</v>
+        <v>240.1</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" s="10" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V44" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="12" t="inlineStr"/>
+      <c r="W44" s="10" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4222,71 +4262,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>168211.1</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>825.1</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>51.7</v>
+        <v>1.8</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.6</v>
+        <v>60.2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2637</v>
+        <v>105.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>183.3</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="L45" s="11" t="n">
-        <v>1910.4</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="K45" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>109.2</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>10092105.9</v>
+        <v>1218.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>34.2</v>
+        <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="11" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="R45" s="11" t="n">
-        <v>129.2</v>
+      <c r="Q45" s="10" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1382</v>
+        <v>138.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V45" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W45" s="11" t="n">
-        <v>182.2</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>24.7</v>
-      </c>
+        <v>1121.5</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>48390.4</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4307,20 +4347,20 @@
       <c r="C46" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="D46" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H46" s="13" t="n">
-        <v>17.6</v>
+      <c r="G46" s="15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>167.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4328,28 +4368,26 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R46" s="9" t="n">
+      <c r="Q46" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4361,13 +4399,13 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="15" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,34 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,13 +777,13 @@
       <c r="C4" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -819,10 +801,10 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -834,10 +816,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -849,10 +831,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="9" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -874,32 +856,32 @@
       <c r="C5" s="3" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="D5" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="L5" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="9" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -911,13 +893,13 @@
       <c r="P5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="15" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -926,10 +908,10 @@
       <c r="U5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -957,13 +939,13 @@
       <c r="C6" s="3" t="n">
         <v>421.6</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -978,13 +960,13 @@
       <c r="J6" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K6" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L6" s="10" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -996,10 +978,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1011,10 +993,10 @@
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="9" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1042,19 +1024,19 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1064,42 +1046,42 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="15" t="n">
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>152.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="10" t="n">
+      <c r="V7" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1125,18 +1107,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1151,10 +1133,10 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1166,10 +1148,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="9" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1181,17 +1163,17 @@
       <c r="U8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>175.2</v>
+        <v>75.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>27</v>
@@ -1212,14 +1194,14 @@
       <c r="C9" s="3" t="n">
         <v>166.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="8" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>822.5</v>
+        <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>6</v>
@@ -1233,13 +1215,13 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L9" s="10" t="n">
+      <c r="K9" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="L9" s="9" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="9" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1251,11 +1233,11 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>138.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1617.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>131.9</v>
@@ -1266,10 +1248,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1279,7 +1261,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1297,13 +1279,13 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1321,13 +1303,13 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="15" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1336,10 +1318,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1351,10 +1333,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1382,13 +1364,13 @@
       <c r="C11" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1406,10 +1388,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1421,14 +1403,14 @@
       <c r="P11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>850.1</v>
@@ -1436,10 +1418,10 @@
       <c r="U11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V11" s="10" t="n">
+      <c r="V11" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="10" t="n">
+      <c r="W11" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1467,20 +1449,20 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1491,10 +1473,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1504,12 +1486,12 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q12" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1521,17 +1503,17 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="10" t="n">
+      <c r="W12" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="15" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1550,15 +1532,15 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1576,10 +1558,10 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1591,10 +1573,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="R13" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1606,10 +1588,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1637,13 +1619,13 @@
       <c r="C14" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1661,10 +1643,10 @@
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="15" t="n">
+      <c r="M14" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1676,10 +1658,10 @@
       <c r="P14" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1688,16 +1670,16 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="15" t="n">
+      <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="V14" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W14" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="15" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1720,15 +1702,15 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>143.3</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="E15" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1746,11 +1728,11 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="15" t="n">
-        <v>29.1</v>
+      <c r="M15" s="9" t="n">
+        <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1761,10 +1743,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1776,13 +1758,13 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="15" t="n">
+      <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
@@ -1805,35 +1787,35 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>992.7</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>149.9</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F16" s="10" t="n">
+      <c r="E16" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>194.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>105.2</v>
@@ -1844,14 +1826,14 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1042.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1859,10 +1841,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="9" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1888,22 +1870,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>399.8</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>28.1</v>
+        <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.2</v>
@@ -1911,10 +1893,10 @@
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K17" s="15" t="n">
-        <v>11551.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="M17" s="9" t="n">
@@ -1929,25 +1911,25 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>73.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="9" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1975,23 +1957,23 @@
       <c r="C18" s="3" t="n">
         <v>431.1</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>4</v>
@@ -1999,25 +1981,25 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
-        <v>20.8</v>
+      <c r="M18" s="9" t="n">
+        <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2029,11 +2011,11 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="10" t="n">
-        <v>25.6</v>
+      <c r="W18" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
@@ -2058,22 +2040,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2223.4</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
@@ -2084,10 +2066,10 @@
       <c r="K19" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="15" t="n">
+      <c r="M19" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2099,10 +2081,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="Q19" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2114,10 +2096,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="10" t="n">
+      <c r="W19" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2145,34 +2127,34 @@
       <c r="C20" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="L20" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2184,11 +2166,11 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="17" t="n">
-        <v>24.15</v>
+      <c r="R20" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2199,10 +2181,10 @@
       <c r="U20" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V20" s="10" t="n">
+      <c r="V20" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="10" t="n">
+      <c r="W20" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2230,13 +2212,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2254,10 +2236,10 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2269,25 +2251,25 @@
       <c r="P21" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="10" t="n">
+      <c r="W21" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2297,7 +2279,7 @@
         <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2313,18 +2295,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2374.6</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="G22" s="15" t="n">
+      <c r="F22" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2339,11 +2321,11 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="15" t="n">
-        <v>26.2</v>
+      <c r="M22" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2354,25 +2336,25 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2398,33 +2380,33 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="9" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="9" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="L23" s="10" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>95.2</v>
       </c>
       <c r="M23" s="9" t="n">
@@ -2437,9 +2419,9 @@
         <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="Q23" s="10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>146.2</v>
       </c>
       <c r="R23" s="9" t="n">
@@ -2449,12 +2431,12 @@
         <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2895.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="9" t="n">
         <v>122.2</v>
       </c>
       <c r="W23" s="9" t="n">
@@ -2464,10 +2446,10 @@
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2483,22 +2465,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1398.5</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v>67.59999999999999</v>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2509,14 +2491,14 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2524,7 +2506,7 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="9" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="9" t="n">
@@ -2537,12 +2519,12 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="V24" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2568,15 +2550,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2374</v>
-      </c>
-      <c r="D25" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2594,10 +2576,10 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2607,16 +2589,16 @@
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="9" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
@@ -2624,20 +2606,20 @@
       <c r="U25" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" s="10" t="n">
+      <c r="V25" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="15" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>174.8</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2655,13 +2637,13 @@
       <c r="C26" s="3" t="n">
         <v>329.8</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2679,10 +2661,10 @@
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2694,10 +2676,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2707,22 +2689,22 @@
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="15" t="n">
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,25 +2720,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1354.4</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2764,25 +2746,25 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2791,13 +2773,13 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="15" t="n">
+      <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V27" s="10" t="n">
+      <c r="V27" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="W27" s="10" t="n">
+      <c r="W27" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2825,13 +2807,13 @@
       <c r="C28" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2849,10 +2831,10 @@
       <c r="K28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2864,10 +2846,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2879,10 +2861,10 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="V28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2910,37 +2892,37 @@
       <c r="C29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="D29" s="9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L29" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="15" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
@@ -2949,10 +2931,10 @@
       <c r="P29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="R29" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2964,10 +2946,10 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="9" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2993,22 +2975,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1856</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>150.3</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>91.2</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.7</v>
+        <v>91.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -3016,13 +2998,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="10" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="M30" s="10" t="n">
+      <c r="L30" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="M30" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3034,10 +3016,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>138.5</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="9" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,12 +3029,12 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V30" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V30" s="9" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="9" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3080,34 +3062,34 @@
       <c r="C31" s="3" t="n">
         <v>37.1</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="10" t="n">
+      <c r="D31" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3119,25 +3101,25 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="15" t="n">
+      <c r="S31" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="10" t="n">
+      <c r="V31" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="9" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3163,39 +3145,39 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G32" s="15" t="n">
+      <c r="F32" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3204,10 +3186,10 @@
       <c r="P32" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="9" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3219,17 +3201,17 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="10" t="n">
+      <c r="V32" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3248,16 +3230,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.9</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>26.8</v>
+        <v>397</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>13.9</v>
@@ -3271,13 +3253,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3289,25 +3271,25 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>147.7</v>
+        <v>47.7</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="10" t="n">
+      <c r="V33" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3317,7 +3299,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3333,22 +3315,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1362.4</v>
-      </c>
-      <c r="D34" s="10" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
@@ -3356,13 +3338,13 @@
       <c r="J34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3374,10 +3356,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="9" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3389,17 +3371,17 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="10" t="n">
+      <c r="V34" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="10" t="n">
+      <c r="W34" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3420,14 +3402,14 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>22.6</v>
+      <c r="D35" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>3.9</v>
@@ -3441,17 +3423,17 @@
       <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M35" s="10" t="n">
+      <c r="L35" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="M35" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3459,10 +3441,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3474,10 +3456,10 @@
       <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3505,19 +3487,19 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3526,13 +3508,13 @@
       <c r="J36" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3544,10 +3526,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="10" t="n">
+      <c r="R36" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3559,10 +3541,10 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="10" t="n">
+      <c r="V36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W36" s="10" t="n">
+      <c r="W36" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3588,19 +3570,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>1683.5</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>100.9</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>149.2</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3612,12 +3594,12 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>102.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="9" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3629,10 +3611,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="9" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="9" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3644,10 +3626,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3673,15 +3655,15 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2326.7</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3691,7 +3673,7 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
@@ -3699,11 +3681,11 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>21.4</v>
@@ -3714,10 +3696,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3729,10 +3711,10 @@
       <c r="U38" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="V38" s="10" t="n">
+      <c r="V38" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3758,15 +3740,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D39" s="10" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3779,18 +3761,18 @@
         <v>2.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="15" t="n">
+      <c r="N39" s="3" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3799,10 +3781,10 @@
       <c r="P39" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="R39" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3814,10 +3796,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="10" t="n">
+      <c r="V39" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="10" t="n">
+      <c r="W39" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3845,20 +3827,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="E40" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F40" s="10" t="n">
+      <c r="E40" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>129</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3867,12 +3849,12 @@
         <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L40" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L40" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3884,10 +3866,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3899,10 +3881,10 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="10" t="n">
+      <c r="V40" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3928,19 +3910,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>244.8</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E41" s="17" t="n">
+        <v>448.8</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E41" s="13" t="n">
         <v>1.9</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17.4</v>
@@ -3954,10 +3936,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3969,10 +3951,10 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3984,10 +3966,10 @@
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4013,18 +3995,18 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="D42" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4039,10 +4021,10 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="10" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M42" s="10" t="n">
+      <c r="L42" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M42" s="9" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4054,25 +4036,25 @@
       <c r="P42" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4098,18 +4080,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4124,28 +4106,28 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>188.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="15" t="n">
+      <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4154,11 +4136,11 @@
       <c r="U43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="10" t="n">
-        <v>22.4</v>
+      <c r="W43" s="9" t="n">
+        <v>21.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4167,7 +4149,7 @@
         <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4185,13 +4167,13 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4207,16 +4189,16 @@
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L44" s="10" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L44" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="N44" s="15" t="n">
-        <v>4.1</v>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>240.1</v>
@@ -4224,10 +4206,10 @@
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4237,12 +4219,12 @@
         <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="V44" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V44" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr"/>
@@ -4264,13 +4246,13 @@
       <c r="C45" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="9" t="n">
         <v>174</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>113.8</v>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="9" t="n">
         <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4285,48 +4267,48 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="M45" s="10" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="M45" s="9" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1218.1</v>
+        <v>121.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="Q45" s="10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>157.5</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="9" t="n">
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>424</v>
+        <v>14</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="V45" s="9" t="n">
         <v>145.5</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>231.2</v>
+      <c r="W45" s="8" t="n">
+        <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>48390.4</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4345,22 +4327,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F46" s="10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>167.6</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4368,26 +4350,28 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4399,13 +4383,13 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="15" t="n">
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -35,12 +35,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
@@ -55,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -149,19 +149,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,13 +777,13 @@
       <c r="C4" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -801,10 +801,10 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -816,10 +816,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -831,10 +831,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -856,13 +856,13 @@
       <c r="C5" s="3" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -878,10 +878,10 @@
       <c r="K5" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -893,10 +893,10 @@
       <c r="P5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -908,10 +908,10 @@
       <c r="U5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -939,13 +939,13 @@
       <c r="C6" s="3" t="n">
         <v>421.6</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -963,10 +963,10 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -978,10 +978,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -993,10 +993,10 @@
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1024,13 +1024,13 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1048,10 +1048,10 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>16</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1063,10 +1063,10 @@
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1078,10 +1078,10 @@
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1109,13 +1109,13 @@
       <c r="C8" s="3" t="n">
         <v>297.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1133,10 +1133,10 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1148,10 +1148,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1163,10 +1163,10 @@
       <c r="U8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1195,12 +1195,12 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>252.6</v>
+        <v>152.6</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>92.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1215,28 +1215,28 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="L9" s="9" t="n">
+      <c r="K9" s="13" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>22.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1248,10 +1248,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1261,7 +1261,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1303,10 +1303,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M10" s="9" t="n">
+      <c r="L10" s="13" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M10" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1318,10 +1318,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1333,10 +1333,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1364,13 +1364,13 @@
       <c r="C11" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1388,10 +1388,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1403,10 +1403,10 @@
       <c r="P11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1418,10 +1418,10 @@
       <c r="U11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1449,13 +1449,13 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1473,10 +1473,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1488,10 +1488,10 @@
       <c r="P12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1503,10 +1503,10 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1534,13 +1534,13 @@
       <c r="C13" s="3" t="n">
         <v>35.6</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1558,10 +1558,10 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1573,10 +1573,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1588,10 +1588,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1617,15 +1617,15 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>374</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1643,10 +1643,10 @@
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1658,10 +1658,10 @@
       <c r="P14" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1673,10 +1673,10 @@
       <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1704,13 +1704,13 @@
       <c r="C15" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1728,10 +1728,10 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1743,10 +1743,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1758,10 +1758,10 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1787,15 +1787,15 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>992.7</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="D16" s="8" t="n">
         <v>149.9</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1811,10 +1811,10 @@
         <v>15.8</v>
       </c>
       <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="8" t="n">
+      <c r="L16" s="13" t="n">
         <v>1.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1826,10 +1826,10 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1841,10 +1841,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="8" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1872,13 +1872,13 @@
       <c r="C17" s="3" t="n">
         <v>39.8</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1896,10 +1896,10 @@
       <c r="K17" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1911,10 +1911,10 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1926,10 +1926,10 @@
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1957,13 +1957,13 @@
       <c r="C18" s="3" t="n">
         <v>431.1</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1981,10 +1981,10 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1994,12 +1994,12 @@
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2011,10 +2011,10 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2040,15 +2040,15 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>223.4</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2066,10 +2066,10 @@
       <c r="K19" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2081,10 +2081,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2096,10 +2096,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2127,13 +2127,13 @@
       <c r="C20" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2151,10 +2151,10 @@
       <c r="K20" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2166,11 +2166,11 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="9" t="n">
-        <v>21.5</v>
+      <c r="R20" s="8" t="n">
+        <v>22.15</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2181,10 +2181,10 @@
       <c r="U20" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2212,13 +2212,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2234,12 +2234,12 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L21" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2251,25 +2251,25 @@
       <c r="P21" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2297,13 +2297,13 @@
       <c r="C22" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2321,10 +2321,10 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2336,10 +2336,10 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2351,10 +2351,10 @@
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2382,13 +2382,13 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2401,15 +2401,15 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="K23" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K23" s="13" t="n">
         <v>49.2</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="8" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2421,10 +2421,10 @@
       <c r="P23" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>146.2</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="13" t="n">
         <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2436,20 +2436,20 @@
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>122.2</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>11</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2467,20 +2467,20 @@
       <c r="C24" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2489,12 +2489,12 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2506,10 +2506,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2519,12 +2519,12 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2552,13 +2552,13 @@
       <c r="C25" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2574,12 +2574,12 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L25" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2591,10 +2591,10 @@
       <c r="P25" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2606,10 +2606,10 @@
       <c r="U25" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2637,20 +2637,20 @@
       <c r="C26" s="3" t="n">
         <v>329.8</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
@@ -2661,10 +2661,10 @@
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2676,10 +2676,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2691,10 +2691,10 @@
       <c r="U26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2722,13 +2722,13 @@
       <c r="C27" s="3" t="n">
         <v>354.8</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2746,10 +2746,10 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2761,10 +2761,10 @@
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2776,10 +2776,10 @@
       <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2807,13 +2807,13 @@
       <c r="C28" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2831,10 +2831,10 @@
       <c r="K28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2846,10 +2846,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2861,10 +2861,10 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2890,15 +2890,15 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D29" s="9" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2908,7 +2908,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2916,10 +2916,10 @@
       <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2931,10 +2931,10 @@
       <c r="P29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2946,10 +2946,10 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2975,22 +2975,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856</v>
-      </c>
-      <c r="D30" s="8" t="n">
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="13" t="n">
         <v>150.3</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="13" t="n">
         <v>91.2</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2998,13 +2998,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K30" s="13" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L30" s="13" t="n">
         <v>29.6</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3016,10 +3016,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>138.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3031,10 +3031,10 @@
       <c r="U30" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="8" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3062,13 +3062,13 @@
       <c r="C31" s="3" t="n">
         <v>37.1</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3086,10 +3086,10 @@
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="13" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3101,10 +3101,10 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3116,10 +3116,10 @@
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="8" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3147,13 +3147,13 @@
       <c r="C32" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3168,13 +3168,13 @@
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3186,10 +3186,10 @@
       <c r="P32" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3201,10 +3201,10 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3232,13 +3232,13 @@
       <c r="C33" s="3" t="n">
         <v>397</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>33.7</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3253,13 +3253,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3271,10 +3271,10 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3286,10 +3286,10 @@
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3317,13 +3317,13 @@
       <c r="C34" s="3" t="n">
         <v>362.4</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3338,13 +3338,13 @@
       <c r="J34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3356,10 +3356,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3371,10 +3371,10 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3402,13 +3402,13 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3423,13 +3423,13 @@
       <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3441,10 +3441,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3456,10 +3456,10 @@
       <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3487,13 +3487,13 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3508,13 +3508,13 @@
       <c r="J36" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3526,10 +3526,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3541,10 +3541,10 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3572,13 +3572,13 @@
       <c r="C37" s="3" t="n">
         <v>1683.5</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3593,13 +3593,13 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3611,10 +3611,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="8" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3626,10 +3626,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3657,13 +3657,13 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3679,12 +3679,12 @@
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3696,10 +3696,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R38" s="9" t="n">
+      <c r="Q38" s="13" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3709,12 +3709,12 @@
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3742,14 +3742,14 @@
       <c r="C39" s="3" t="n">
         <v>400.8</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>25.6</v>
+      <c r="D39" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12.3</v>
@@ -3763,13 +3763,13 @@
       <c r="J39" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3781,10 +3781,10 @@
       <c r="P39" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3796,10 +3796,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3827,14 +3827,14 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>22.1</v>
+      <c r="D40" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>22.21</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3848,13 +3848,13 @@
       <c r="J40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L40" s="9" t="n">
+      <c r="K40" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3866,10 +3866,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3881,10 +3881,10 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3910,15 +3910,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.8</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F41" s="9" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3933,13 +3933,13 @@
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3951,25 +3951,25 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>57.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -3995,15 +3995,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="D42" s="9" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="D42" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4018,13 +4018,13 @@
       <c r="J42" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4036,10 +4036,10 @@
       <c r="P42" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4051,10 +4051,10 @@
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4082,13 +4082,13 @@
       <c r="C43" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4103,13 +4103,13 @@
       <c r="J43" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4121,10 +4121,10 @@
       <c r="P43" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4136,11 +4136,11 @@
       <c r="U43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>21.4</v>
+      <c r="W43" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4167,14 +4167,14 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>21.4</v>
+      <c r="E44" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4188,14 +4188,14 @@
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="9" t="n">
-        <v>18.2</v>
+      <c r="M44" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4206,10 +4206,10 @@
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4221,10 +4221,10 @@
       <c r="U44" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="V44" s="9" t="n">
+      <c r="V44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="9" t="n">
+      <c r="W44" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr"/>
@@ -4246,13 +4246,13 @@
       <c r="C45" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="8" t="n">
         <v>174</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>113.8</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4270,10 +4270,10 @@
       <c r="K45" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>116.4</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="13" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4285,30 +4285,30 @@
       <c r="P45" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>14</v>
+        <v>414</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>71.5</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="W45" s="8" t="n">
+      <c r="W45" s="13" t="n">
         <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4327,15 +4327,15 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F46" s="9" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4351,12 +4351,12 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="13" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4368,11 +4368,11 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>21.6</v>
+      <c r="R46" s="13" t="n">
+        <v>221.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
@@ -4383,10 +4383,10 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -799,7 +799,7 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>17.6</v>
@@ -1216,7 +1216,7 @@
         <v>15.5</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>44.2</v>
+        <v>442.5</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>94.3</v>
@@ -1228,7 +1228,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22.2</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1301,7 +1301,7 @@
         <v>3.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>18.2</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.6</v>
+        <v>19.9</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>149.9</v>
@@ -1894,7 +1894,7 @@
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>20.2</v>
@@ -1978,7 +1978,7 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2063,7 +2063,7 @@
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="L19" s="8" t="n">
@@ -2143,12 +2143,12 @@
         <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>24</v>
       </c>
       <c r="L20" s="8" t="n">
@@ -2170,7 +2170,7 @@
         <v>25.5</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>22.15</v>
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2233,8 +2233,8 @@
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.6</v>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>18.8</v>
@@ -2318,7 +2318,7 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2403,7 +2403,7 @@
       <c r="J23" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="8" t="n">
         <v>49.2</v>
       </c>
       <c r="L23" s="8" t="n">
@@ -2424,7 +2424,7 @@
       <c r="Q23" s="8" t="n">
         <v>146.2</v>
       </c>
-      <c r="R23" s="13" t="n">
+      <c r="R23" s="8" t="n">
         <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2480,7 +2480,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2573,10 +2573,10 @@
       <c r="J25" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
+      <c r="K25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="8" t="n">
@@ -2619,7 +2619,7 @@
         <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
       <c r="J26" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="8" t="n">
@@ -2743,10 +2743,10 @@
       <c r="J27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="8" t="n">
@@ -2828,10 +2828,10 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="M28" s="8" t="n">
@@ -2913,10 +2913,10 @@
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="M29" s="8" t="n">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
+        <v>185.6</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>150.3</v>
@@ -2990,7 +2990,7 @@
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2998,11 +2998,11 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="13" t="n">
-        <v>29.6</v>
+      <c r="L30" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>93.2</v>
@@ -3029,7 +3029,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>123.1</v>
@@ -3084,7 +3084,7 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="n">
         <v>19.2</v>
@@ -3175,7 +3175,7 @@
         <v>20.6</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>21.5</v>
@@ -3211,7 +3211,7 @@
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3433,7 +3433,7 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>398.9</v>
+        <v>39.8</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>28.6</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
+        <v>168.5</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>150.1</v>
@@ -3599,7 +3599,7 @@
       <c r="L37" s="8" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="13" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3611,8 +3611,8 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="8" t="n">
-        <v>139.6</v>
+      <c r="Q37" s="13" t="n">
+        <v>189.6</v>
       </c>
       <c r="R37" s="8" t="n">
         <v>115.4</v>
@@ -3673,13 +3673,13 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>20.7</v>
@@ -3696,8 +3696,8 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="13" t="n">
-        <v>27.2</v>
+      <c r="Q38" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>23.1</v>
@@ -3769,7 +3769,7 @@
       <c r="L39" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3834,7 +3834,7 @@
         <v>20.2</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>22.21</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3854,11 +3854,11 @@
       <c r="L40" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.2</v>
+        <v>448.8</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>19.5</v>
@@ -3939,7 +3939,7 @@
       <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3961,7 +3961,7 @@
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>57.4</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.2</v>
+        <v>46.4</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>32.8</v>
@@ -4024,7 +4024,7 @@
       <c r="L42" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="8" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4109,7 +4109,7 @@
       <c r="L43" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4194,8 +4194,8 @@
       <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>28.2</v>
+      <c r="M44" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4273,8 +4273,8 @@
       <c r="L45" s="8" t="n">
         <v>116.4</v>
       </c>
-      <c r="M45" s="13" t="n">
-        <v>109.2</v>
+      <c r="M45" s="8" t="n">
+        <v>109.3</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>121.1</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4333,7 +4333,7 @@
         <v>29</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>24</v>
@@ -4351,12 +4351,12 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="13" t="n">
+      <c r="M46" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4371,8 +4371,8 @@
       <c r="Q46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="13" t="n">
-        <v>221.6</v>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,7 +795,7 @@
       <c r="J4" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -869,7 +878,7 @@
       <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>25.8</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -952,7 +961,7 @@
         <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1037,7 +1046,7 @@
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1122,7 +1131,7 @@
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1207,7 +1216,7 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1375,7 +1384,7 @@
       <c r="J11" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1458,7 +1467,7 @@
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1543,7 +1552,7 @@
       <c r="J13" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1628,7 +1637,7 @@
       <c r="J14" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="10" t="n">
         <v>5.7</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1713,7 +1722,7 @@
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1798,7 +1807,7 @@
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2385,7 +2394,7 @@
       <c r="J23" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>3.7</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2980,7 +2989,7 @@
       <c r="J30" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3150,7 +3159,7 @@
       <c r="J32" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="12" t="n"/>
       <c r="L32" s="3" t="n">
         <v>19.9</v>
       </c>
@@ -3573,7 +3582,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4253,7 +4262,7 @@
       <c r="J45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L45" s="3" t="n">
